--- a/backend/sample_templates/standard_inspection_v4.xlsx
+++ b/backend/sample_templates/standard_inspection_v4.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one condition</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>overall_condition</t>
+          <t>access_ok</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overall condition</t>
+          <t>Site access OK?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -494,48 +494,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>access_ok</t>
+          <t>grp_form_content</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Site access OK?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>&lt;b&gt;[Form-Specific Content]&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>inspector_notes</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Inspector notes</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>multiline</t>
         </is>

--- a/backend/sample_templates/standard_inspection_v4.xlsx
+++ b/backend/sample_templates/standard_inspection_v4.xlsx
@@ -693,7 +693,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Standard Inspection</t>
+          <t>Standard Inspection v4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
